--- a/GeoMIP/results/resultados_Geometric.xlsx
+++ b/GeoMIP/results/resultados_Geometric.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,32 +417,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Iteración</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Alcance</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Mecanismo</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Partición</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Pérdida</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Tiempo de ejecución (s)</t>
         </is>
@@ -474,9 +462,22 @@
           <t>111111111111111</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>| ∅ || A,B,C,D,E,F,G,H,I,J,K,L,M,N,O |
+| i ||  a,b,c,d,e,f,g,h,j,k,l,m,n,o  |</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>151,8815655708313</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -492,9 +493,22 @@
           <t>111111111111111</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>| ∅ || A,B,C,D,E,F,G,H,I,J,K,L,M,N,O |
+| i ||  a,b,c,d,e,f,g,h,j,k,l,m,n,o  |</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>135,1290557384491</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -510,9 +524,22 @@
           <t>011111111111111</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>| ∅ || A,B,C,D,E,F,G,H,I,J,K,L,M,N,O |
+| o ||   b,c,d,e,f,g,h,i,j,k,l,m,n   |</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>57,72796607017517</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -528,9 +555,22 @@
           <t>011111111111111</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>| ∅ || A,B,C,D,E,F,G,H,I,J,K,L,M,N,O |
+| o ||   b,c,d,e,f,g,h,i,j,k,l,m,n   |</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>58,36933135986328</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -546,9 +586,22 @@
           <t>101010101010101</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>| L || A,B,C,D,E,F,G,H,I,J,K,M,N,O |
+| ∅ ||       a,c,e,g,i,k,m,o       |</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0,0041897893</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>11,960881233215332</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -564,9 +617,22 @@
           <t>010101010101010</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>| G || A,B,C,D,E,F,H,I,J,K,L,M,N,O |
+| ∅ ||        b,d,f,h,j,l,n        |</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0,0070973635</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>10,755889892578125</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -582,9 +648,22 @@
           <t>110110110110110</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>| O || A,B,C,D,E,F,G,H,I,J,K,L,M,N |
+| ∅ ||     a,b,d,e,g,h,j,k,m,n     |</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>4,7147274e-05</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>20,030361652374268</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -600,9 +679,22 @@
           <t>111111111111111</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>| ∅ || A,B,C,D,E,F,G,H,I,J,K,L,M,N,O |
+| i ||  a,b,c,d,e,f,g,h,j,k,l,m,n,o  |</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>133,398104429245</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -618,9 +710,22 @@
           <t>111111111111111</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>| ∅ || A,B,C,D,E,F,G,H,I,J,K,L,M,N,O |
+| i ||  a,b,c,d,e,f,g,h,j,k,l,m,n,o  |</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>116,88214159011841</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -636,9 +741,22 @@
           <t>011111111111111</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>| ∅ || A,B,C,D,E,F,G,H,I,J,K,L,M,N,O |
+| o ||   b,c,d,e,f,g,h,i,j,k,l,m,n   |</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>53,941582918167114</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -654,9 +772,22 @@
           <t>011111111111111</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>| ∅ || A,B,C,D,E,F,G,H,I,J,K,L,M,N,O |
+| o ||   b,c,d,e,f,g,h,i,j,k,l,m,n   |</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>52,67555379867554</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -672,9 +803,22 @@
           <t>101010101010101</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>| L || A,B,C,D,E,F,G,H,I,J,K,M,N,O |
+| ∅ ||       a,c,e,g,i,k,m,o       |</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0,0041897893</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>12,779444932937622</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -690,9 +834,22 @@
           <t>010101010101010</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>| G || A,B,C,D,E,F,H,I,J,K,L,M,N,O |
+| ∅ ||        b,d,f,h,j,l,n        |</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0,0070973635</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>10,088547468185425</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -708,9 +865,22 @@
           <t>110110110110110</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>| O || A,B,C,D,E,F,G,H,I,J,K,L,M,N |
+| ∅ ||     a,b,d,e,g,h,j,k,m,n     |</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>4,7147274e-05</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>17,007323503494263</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -726,9 +896,22 @@
           <t>111111111111111</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>| ∅ || B,C,D,E,F,G,H,I,J,K,L,M,N,O |
+| o || a,b,c,d,e,f,g,h,i,j,k,l,m,n |</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>99,53244972229004</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -744,9 +927,22 @@
           <t>111111111111111</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>| ∅ || B,C,D,E,F,G,H,I,J,K,L,M,N,O |
+| o || a,b,c,d,e,f,g,h,i,j,k,l,m,n |</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>93,49926400184631</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -762,9 +958,22 @@
           <t>011111111111111</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>| ∅ || B,C,D,E,F,G,H,I,J,K,L,M,N,O |
+| o ||  b,c,d,e,f,g,h,i,j,k,l,m,n  |</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>43,506261110305786</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -780,9 +989,22 @@
           <t>011111111111111</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>| ∅ || B,C,D,E,F,G,H,I,J,K,L,M,N,O |
+| o ||  b,c,d,e,f,g,h,i,j,k,l,m,n  |</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>51,830557107925415</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -798,9 +1020,22 @@
           <t>101010101010101</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>| L || B,C,D,E,F,G,H,I,J,K,M,N,O |
+| ∅ ||      a,c,e,g,i,k,m,o      |</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0,0041897893</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>11,917392492294312</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -816,9 +1051,22 @@
           <t>010101010101010</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>| G || B,C,D,E,F,H,I,J,K,L,M,N,O |
+| ∅ ||       b,d,f,h,j,l,n       |</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0,0070973635</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>10,224176168441772</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -834,9 +1082,22 @@
           <t>110110110110110</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>| O || B,C,D,E,F,G,H,I,J,K,L,M,N |
+| ∅ ||    a,b,d,e,g,h,j,k,m,n    |</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>4,7147274e-05</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>14,068840503692627</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -852,9 +1113,22 @@
           <t>111111111111111</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>| ∅ || B,C,D,E,F,G,H,I,J,K,L,M,N,O |
+| o || a,b,c,d,e,f,g,h,i,j,k,l,m,n |</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>103,1250696182251</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -870,9 +1144,22 @@
           <t>111111111111111</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>| ∅ || B,C,D,E,F,G,H,I,J,K,L,M,N,O |
+| o || a,b,c,d,e,f,g,h,i,j,k,l,m,n |</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>104,39413332939148</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -888,9 +1175,22 @@
           <t>011111111111111</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>| ∅ || B,C,D,E,F,G,H,I,J,K,L,M,N,O |
+| o ||  b,c,d,e,f,g,h,i,j,k,l,m,n  |</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>57,44953012466431</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -906,9 +1206,22 @@
           <t>011111111111111</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>| ∅ || B,C,D,E,F,G,H,I,J,K,L,M,N,O |
+| o ||  b,c,d,e,f,g,h,i,j,k,l,m,n  |</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>54,54828476905823</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -924,9 +1237,22 @@
           <t>101010101010101</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>| L || B,C,D,E,F,G,H,I,J,K,M,N,O |
+| ∅ ||      a,c,e,g,i,k,m,o      |</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0,0041897893</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>9,970965385437012</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -942,9 +1268,22 @@
           <t>010101010101010</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>| G || B,C,D,E,F,H,I,J,K,L,M,N,O |
+| ∅ ||       b,d,f,h,j,l,n       |</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0,0070973635</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>8,311559438705444</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -960,9 +1299,22 @@
           <t>110110110110110</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>| O || B,C,D,E,F,G,H,I,J,K,L,M,N |
+| ∅ ||    a,b,d,e,g,h,j,k,m,n    |</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>4,7147274e-05</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>13,571430683135986</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -978,9 +1330,22 @@
           <t>111111111111111</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>| ∅ ||       A,C,E,G,I,K,M,O       |
+| i || a,b,c,d,e,f,g,h,j,k,l,m,n,o |</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>33,85934233665466</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -996,9 +1361,22 @@
           <t>111111111111111</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>| ∅ ||       A,C,E,G,I,K,M,O       |
+| i || a,b,c,d,e,f,g,h,j,k,l,m,n,o |</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>35,8164427280426</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1014,9 +1392,22 @@
           <t>011111111111111</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>| ∅ ||      A,C,E,G,I,K,M,O      |
+| o || b,c,d,e,f,g,h,i,j,k,l,m,n |</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>18,30118441581726</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1032,9 +1423,22 @@
           <t>011111111111111</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>| ∅ ||      A,C,E,G,I,K,M,O      |
+| o || b,c,d,e,f,g,h,i,j,k,l,m,n |</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>17,115434885025024</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1050,9 +1454,22 @@
           <t>101010101010101</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>| E ||  A,C,G,I,K,M,O  |
+| ∅ || a,c,e,g,i,k,m,o |</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0,005357504</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2,8968505859375</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1068,9 +1485,22 @@
           <t>010101010101010</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>| G || A,C,E,I,K,M,O |
+| ∅ || b,d,f,h,j,l,n |</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0,0070973635</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2,126020669937134</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1086,9 +1516,22 @@
           <t>110110110110110</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>| O ||    A,C,E,G,I,K,M    |
+| ∅ || a,b,d,e,g,h,j,k,m,n |</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>4,7147274e-05</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>4,245934247970581</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1104,9 +1547,22 @@
           <t>111111111111111</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>| ∅ ||        B,D,F,H,J,L,N        |
+| i || a,b,c,d,e,f,g,h,j,k,l,m,n,o |</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>30,134520292282104</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1122,9 +1578,22 @@
           <t>111111111111111</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>| ∅ ||        B,D,F,H,J,L,N        |
+| i || a,b,c,d,e,f,g,h,j,k,l,m,n,o |</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>28,023497343063354</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1140,9 +1609,22 @@
           <t>011111111111111</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>| ∅ ||       B,D,F,H,J,L,N       |
+| o || b,c,d,e,f,g,h,i,j,k,l,m,n |</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>14,340684175491333</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1158,9 +1640,22 @@
           <t>011111111111111</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>| ∅ ||       B,D,F,H,J,L,N       |
+| o || b,c,d,e,f,g,h,i,j,k,l,m,n |</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>12,14661169052124</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1176,9 +1671,22 @@
           <t>101010101010101</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>| L ||   B,D,F,H,J,N   |
+| ∅ || a,c,e,g,i,k,m,o |</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0,0041897893</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1,9367713928222656</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1194,9 +1702,22 @@
           <t>010101010101010</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>| N ||  B,D,F,H,J,L  |
+| ∅ || b,d,f,h,j,l,n |</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0,008794069</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1,4770426750183105</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1212,9 +1733,22 @@
           <t>110110110110110</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>| N ||     B,D,F,H,J,L     |
+| ∅ || a,b,d,e,g,h,j,k,m,n |</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0,0013378263</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>3,106539726257324</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1230,9 +1764,22 @@
           <t>111111111111111</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>| ∅ ||     A,B,D,E,G,H,J,K,M,N     |
+| o || a,b,c,d,e,f,g,h,i,j,k,l,m,n |</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>45,15028381347656</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1248,9 +1795,22 @@
           <t>111111111111111</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>| ∅ ||     A,B,D,E,G,H,J,K,M,N     |
+| o || a,b,c,d,e,f,g,h,i,j,k,l,m,n |</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>46,71605134010315</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1266,9 +1826,22 @@
           <t>011111111111111</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>| ∅ ||    A,B,D,E,G,H,J,K,M,N    |
+| o || b,c,d,e,f,g,h,i,j,k,l,m,n |</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>20,39578151702881</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1284,9 +1857,22 @@
           <t>011111111111111</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>| ∅ ||    A,B,D,E,G,H,J,K,M,N    |
+| o || b,c,d,e,f,g,h,i,j,k,l,m,n |</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>20,42004919052124</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1302,9 +1888,22 @@
           <t>101010101010101</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>| E || A,B,D,G,H,J,K,M,N |
+| ∅ ||  a,c,e,g,i,k,m,o  |</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0,0043781996</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>4,3898022174835205</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1320,9 +1919,22 @@
           <t>010101010101010</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>| G || A,B,D,E,H,J,K,M,N |
+| ∅ ||   b,d,f,h,j,l,n   |</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0,0070973635</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>4,382361650466919</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1338,9 +1950,22 @@
           <t>110110110110110</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>| N ||  A,B,D,E,G,H,J,K,M  |
+| ∅ || a,b,d,e,g,h,j,k,m,n |</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0,0013378263</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>6,6511571407318115</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1356,9 +1981,22 @@
           <t>101111111111111</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>| ∅ || A,C,D,E,F,G,H,I,J,K,L,M,N,O |
+| j ||  a,c,d,e,f,g,h,i,k,l,m,n,o  |</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>47,408283948898315</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
